--- a/Stats Sheet/Round Gaps/The Melon Blooded.xlsx
+++ b/Stats Sheet/Round Gaps/The Melon Blooded.xlsx
@@ -142,6 +142,12 @@
     <x:t>42</x:t>
   </x:si>
   <x:si>
+    <x:t>43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>44</x:t>
+  </x:si>
+  <x:si>
     <x:t>AtomicAdam10</x:t>
   </x:si>
   <x:si>
@@ -262,6 +268,9 @@
     <x:t>168</x:t>
   </x:si>
   <x:si>
+    <x:t>GutinGongoozler</x:t>
+  </x:si>
+  <x:si>
     <x:t>Ledwidgez</x:t>
   </x:si>
   <x:si>
@@ -292,6 +301,9 @@
     <x:t>882</x:t>
   </x:si>
   <x:si>
+    <x:t>219</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sinuar</x:t>
   </x:si>
   <x:si>
@@ -307,9 +319,6 @@
     <x:t>332</x:t>
   </x:si>
   <x:si>
-    <x:t>UltimateVillager</x:t>
-  </x:si>
-  <x:si>
     <x:t>Vesyll</x:t>
   </x:si>
   <x:si>
@@ -382,9 +391,6 @@
     <x:t>1003</x:t>
   </x:si>
   <x:si>
-    <x:t>44</x:t>
-  </x:si>
-  <x:si>
     <x:t>HeyitsDan</x:t>
   </x:si>
   <x:si>
@@ -544,21 +550,21 @@
     <x:t>Big_Z60</x:t>
   </x:si>
   <x:si>
+    <x:t>Brocketships</x:t>
+  </x:si>
+  <x:si>
+    <x:t>221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>163</x:t>
+  </x:si>
+  <x:si>
     <x:t>FlightVapeHacker</x:t>
   </x:si>
   <x:si>
     <x:t>639</x:t>
   </x:si>
   <x:si>
-    <x:t>Honoropz</x:t>
-  </x:si>
-  <x:si>
-    <x:t>221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>163</x:t>
-  </x:si>
-  <x:si>
     <x:t>Lunarashi</x:t>
   </x:si>
   <x:si>
@@ -583,9 +589,6 @@
     <x:t>457</x:t>
   </x:si>
   <x:si>
-    <x:t>Andraea</x:t>
-  </x:si>
-  <x:si>
     <x:t>Aupho</x:t>
   </x:si>
   <x:si>
@@ -598,6 +601,9 @@
     <x:t>3094</x:t>
   </x:si>
   <x:si>
+    <x:t>Mintiie</x:t>
+  </x:si>
+  <x:si>
     <x:t>Scyles</x:t>
   </x:si>
   <x:si>
@@ -790,9 +796,6 @@
     <x:t>106</x:t>
   </x:si>
   <x:si>
-    <x:t>219</x:t>
-  </x:si>
-  <x:si>
     <x:t>161</x:t>
   </x:si>
   <x:si>
@@ -847,6 +850,9 @@
     <x:t>111</x:t>
   </x:si>
   <x:si>
+    <x:t>798</x:t>
+  </x:si>
+  <x:si>
     <x:t>chugmitchell</x:t>
   </x:si>
   <x:si>
@@ -883,15 +889,18 @@
     <x:t>102</x:t>
   </x:si>
   <x:si>
+    <x:t>2796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>idfcdean</x:t>
+  </x:si>
+  <x:si>
     <x:t>ItsNickb</x:t>
   </x:si>
   <x:si>
     <x:t>191</x:t>
   </x:si>
   <x:si>
-    <x:t>Plexsy</x:t>
-  </x:si>
-  <x:si>
     <x:t>Potsie</x:t>
   </x:si>
   <x:si>
@@ -937,6 +946,9 @@
     <x:t>1839</x:t>
   </x:si>
   <x:si>
+    <x:t>413</x:t>
+  </x:si>
+  <x:si>
     <x:t>Perzano</x:t>
   </x:si>
   <x:si>
@@ -973,9 +985,6 @@
     <x:t>142</x:t>
   </x:si>
   <x:si>
-    <x:t>CallMeDJ</x:t>
-  </x:si>
-  <x:si>
     <x:t>CanadianWafflez</x:t>
   </x:si>
   <x:si>
@@ -988,6 +997,9 @@
     <x:t>cards4in_</x:t>
   </x:si>
   <x:si>
+    <x:t>DawsonPresent</x:t>
+  </x:si>
+  <x:si>
     <x:t>Drkrai</x:t>
   </x:si>
   <x:si>
@@ -1012,6 +1024,9 @@
     <x:t>2752</x:t>
   </x:si>
   <x:si>
+    <x:t>426</x:t>
+  </x:si>
+  <x:si>
     <x:t>UncleBenFranklin</x:t>
   </x:si>
   <x:si>
@@ -1024,6 +1039,9 @@
     <x:t>2200</x:t>
   </x:si>
   <x:si>
+    <x:t>1088</x:t>
+  </x:si>
+  <x:si>
     <x:t>JoshvsGaming</x:t>
   </x:si>
   <x:si>
@@ -1177,6 +1195,9 @@
     <x:t>Broseph</x:t>
   </x:si>
   <x:si>
+    <x:t>1125</x:t>
+  </x:si>
+  <x:si>
     <x:t>Geckq</x:t>
   </x:si>
   <x:si>
@@ -1291,7 +1312,7 @@
     <x:t>broccoliar</x:t>
   </x:si>
   <x:si>
-    <x:t>gsjan</x:t>
+    <x:t>horayah</x:t>
   </x:si>
   <x:si>
     <x:t>MadmanAxel</x:t>
@@ -1309,6 +1330,9 @@
     <x:t>kirbey</x:t>
   </x:si>
   <x:si>
+    <x:t>964</x:t>
+  </x:si>
+  <x:si>
     <x:t>TheSlimeBrother</x:t>
   </x:si>
   <x:si>
@@ -1366,6 +1390,9 @@
     <x:t>Kingko24</x:t>
   </x:si>
   <x:si>
+    <x:t>811</x:t>
+  </x:si>
+  <x:si>
     <x:t>ModernPine</x:t>
   </x:si>
   <x:si>
@@ -1487,6 +1514,63 @@
   </x:si>
   <x:si>
     <x:t>Zenithu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>_carn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BoltsInCharge</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gamer4God</x:t>
+  </x:si>
+  <x:si>
+    <x:t>grantfaker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JampoJohn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ShootingGoats</x:t>
+  </x:si>
+  <x:si>
+    <x:t>silverteeth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TehBaconBrawlerZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tubesterkake</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bmeista</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CrowJRC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hecticity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HellaJugDish</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Juniati_</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Proffic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Queequa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Silvril</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stravilight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>swishduck</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1845,10 +1929,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:AT285"/>
+  <x:dimension ref="A1:AV304"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:46" s="1" customFormat="1">
+    <x:row r="1" spans="1:48" s="1" customFormat="1">
       <x:c r="E1" s="1">
         <x:v>41856</x:v>
       </x:c>
@@ -1975,8 +2059,14 @@
       <x:c r="AT1" s="1">
         <x:v>45913</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:46">
+      <x:c r="AU1" s="1">
+        <x:v>46119</x:v>
+      </x:c>
+      <x:c r="AV1" s="1">
+        <x:v>46132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:48">
       <x:c r="F2" s="0">
         <x:v>7</x:v>
       </x:c>
@@ -2100,8 +2190,14 @@
       <x:c r="AT2" s="0">
         <x:v>207</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:46">
+      <x:c r="AU2" s="0">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="AV2" s="0">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:48">
       <x:c r="E3" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -2228,13 +2324,19 @@
       <x:c r="AT3" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:46">
+      <x:c r="AU3" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="AV3" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:48">
       <x:c r="A4" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>0</x:v>
@@ -2243,33 +2345,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="V4" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="W4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD4" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AE4" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:48">
       <x:c r="A5" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>0</x:v>
@@ -2278,18 +2380,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:48">
       <x:c r="A6" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>0</x:v>
@@ -2298,176 +2400,182 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="U6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W6" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="X6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AB6" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AE6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AQ6" s="0" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:46">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:48">
       <x:c r="A7" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AA7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AB7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AC7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AE7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AF7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AI7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AJ7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AK7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AL7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AM7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AN7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AO7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AP7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AQ7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AR7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AT7" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU7" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV7" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:48">
       <x:c r="A8" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>0</x:v>
@@ -2476,48 +2584,48 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q8" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="R8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T8" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W8" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="X8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS8" s="0" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:46">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:48">
       <x:c r="A9" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>0</x:v>
@@ -2526,18 +2634,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:46">
+    <x:row r="10" spans="1:48">
       <x:c r="A10" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>0</x:v>
@@ -2546,15 +2654,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:48">
       <x:c r="A11" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>0</x:v>
@@ -2563,66 +2671,66 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="J11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="P11" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="R11" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="Z11" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AA11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD11" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AE11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AF11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH11" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AJ11" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AM11" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AN11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS11" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:46">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:48">
       <x:c r="A12" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>0</x:v>
@@ -2631,27 +2739,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:46">
+        <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:48">
       <x:c r="A13" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>1</x:v>
@@ -2660,18 +2768,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:48">
       <x:c r="A14" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>1</x:v>
@@ -2680,45 +2788,45 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q14" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="R14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W14" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="X14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y14" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:48">
       <x:c r="A15" s="0">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>1</x:v>
@@ -2727,21 +2835,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="M15" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:46">
+        <x:v>78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:48">
       <x:c r="A16" s="0">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>1</x:v>
@@ -2750,21 +2858,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O16" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:46">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:48">
       <x:c r="A17" s="0">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>1</x:v>
@@ -2773,193 +2881,196 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH17" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="AI17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AJ17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AK17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AN17" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:46">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:48">
       <x:c r="A18" s="0">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G18" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="J18" s="0" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="Y18" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="AE18" s="0" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="AS18" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:48">
       <x:c r="A19" s="0">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D19" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F19" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="Y19" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C19" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G19" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:46">
+      <x:c r="AE19" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="AS19" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:48">
       <x:c r="A20" s="0">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>12</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="V20" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="AF20" s="0" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="AH20" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="AJ20" s="0" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="AK20" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="AL20" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="AM20" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="AO20" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="AP20" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="AT20" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:48">
       <x:c r="A21" s="0">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D21" s="0">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F21" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="V21" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="AF21" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="C21" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F21" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G21" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="I21" s="0" t="s">
+      <x:c r="AH21" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="AJ21" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="AK21" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AL21" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AM21" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AO21" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="N21" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="P21" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="R21" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="S21" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="X21" s="0" t="s">
+      <x:c r="AP21" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AT21" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="AC21" s="0" t="s">
+      <x:c r="AV21" s="0" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="AK21" s="0" t="s">
-        <x:v>96</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:46">
+    </x:row>
+    <x:row r="22" spans="1:48">
       <x:c r="A22" s="0">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D22" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F22" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="C22" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F22" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:46">
+      <x:c r="N22" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="P22" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="R22" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="S22" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="X22" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="AC22" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="AK22" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:48">
       <x:c r="A23" s="0">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>1</x:v>
@@ -2968,18 +3079,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS23" s="0" t="s">
-        <x:v>99</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:46">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:48">
       <x:c r="A24" s="0">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>2</x:v>
@@ -2988,15 +3099,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:48">
       <x:c r="A25" s="0">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>2</x:v>
@@ -3005,18 +3116,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="P25" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:46">
+        <x:v>105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:48">
       <x:c r="A26" s="0">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>2</x:v>
@@ -3025,15 +3136,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:48">
       <x:c r="A27" s="0">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>2</x:v>
@@ -3042,18 +3153,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L27" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:46">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:48">
       <x:c r="A28" s="0">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>2</x:v>
@@ -3062,15 +3173,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:48">
       <x:c r="A29" s="0">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>2</x:v>
@@ -3079,42 +3190,42 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K29" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="V29" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="AB29" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AC29" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AE29" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="AJ29" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="AM29" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AN29" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AO29" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:48">
       <x:c r="A30" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>2</x:v>
@@ -3123,15 +3234,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:48">
       <x:c r="A31" s="0">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>2</x:v>
@@ -3140,18 +3251,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L31" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:46">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:48">
       <x:c r="A32" s="0">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>3</x:v>
@@ -3160,21 +3271,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:48">
       <x:c r="A33" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>3</x:v>
@@ -3183,21 +3294,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K33" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="R33" s="0" t="s">
-        <x:v>117</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:46">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:48">
       <x:c r="A34" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>3</x:v>
@@ -3206,15 +3317,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H34" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:48">
       <x:c r="A35" s="0">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>3</x:v>
@@ -3223,27 +3334,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I35" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="K35" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="AJ35" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="AL35" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="I35" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="K35" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="AJ35" s="0" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="AL35" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:46">
+    </x:row>
+    <x:row r="36" spans="1:48">
       <x:c r="A36" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>3</x:v>
@@ -3252,21 +3363,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q36" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="V36" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:46">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:48">
       <x:c r="A37" s="0">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>3</x:v>
@@ -3275,21 +3386,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L37" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="N37" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:46">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:48">
       <x:c r="A38" s="0">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>3</x:v>
@@ -3298,21 +3409,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="H38" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J38" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="K38" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:48">
       <x:c r="A39" s="0">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>3</x:v>
@@ -3321,24 +3432,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="R39" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="W39" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:46">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:48">
       <x:c r="A40" s="0">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>4</x:v>
@@ -3347,33 +3458,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="J40" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="P40" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="Q40" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R40" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U40" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="AD40" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:46">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:48">
       <x:c r="A41" s="0">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>4</x:v>
@@ -3382,24 +3493,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I41" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N41" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="R41" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="W41" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:46">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:48">
       <x:c r="A42" s="0">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>4</x:v>
@@ -3408,18 +3519,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="I42" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>120</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:46">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:48">
       <x:c r="A43" s="0">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>5</x:v>
@@ -3428,122 +3539,128 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J43" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:48">
       <x:c r="A44" s="0">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="M44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="P44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R44" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="S44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AA44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AB44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AC44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AE44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AF44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH44" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AI44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AJ44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AK44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AL44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AN44" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="AO44" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS44" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="AT44" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU44" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV44" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:48">
       <x:c r="A45" s="0">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>5</x:v>
@@ -3552,15 +3669,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J45" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:48">
       <x:c r="A46" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>5</x:v>
@@ -3569,15 +3686,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J46" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:48">
       <x:c r="A47" s="0">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>5</x:v>
@@ -3586,15 +3703,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J47" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:48">
       <x:c r="A48" s="0">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>6</x:v>
@@ -3603,15 +3720,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K48" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:48">
       <x:c r="A49" s="0">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>6</x:v>
@@ -3620,98 +3737,101 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:48">
       <x:c r="A50" s="0">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N50" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="O50" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="P50" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q50" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S50" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="T50" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U50" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V50" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W50" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X50" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y50" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AC50" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="AD50" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AE50" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AF50" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH50" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AK50" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="AL50" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AM50" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AP50" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="AR50" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="AT50" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:46">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="AV50" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:48">
       <x:c r="A51" s="0">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>6</x:v>
@@ -3720,30 +3840,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L51" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N51" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="Q51" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="T51" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="U51" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:48">
       <x:c r="A52" s="0">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>6</x:v>
@@ -3752,15 +3872,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:48">
       <x:c r="A53" s="0">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>6</x:v>
@@ -3769,15 +3889,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:48">
       <x:c r="A54" s="0">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>6</x:v>
@@ -3786,15 +3906,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:48">
       <x:c r="A55" s="0">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>6</x:v>
@@ -3803,15 +3923,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:48">
       <x:c r="A56" s="0">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>6</x:v>
@@ -3820,15 +3940,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:48">
       <x:c r="A57" s="0">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>6</x:v>
@@ -3837,21 +3957,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U57" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="AP57" s="0" t="s">
-        <x:v>163</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:46">
+        <x:v>165</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:48">
       <x:c r="A58" s="0">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>6</x:v>
@@ -3860,81 +3980,81 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="K58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="M58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="N58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="P58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U58" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="V58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y58" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="Z58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AB58" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="AC58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AE58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AI58" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="AJ58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AK58" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AN58" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="AP58" s="0" t="s">
-        <x:v>168</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:46">
+        <x:v>170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:48">
       <x:c r="A59" s="0">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>6</x:v>
@@ -3943,15 +4063,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K59" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:48">
       <x:c r="A60" s="0">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>6</x:v>
@@ -3960,18 +4080,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K60" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="L60" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:48">
       <x:c r="A61" s="0">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
         <x:v>6</x:v>
@@ -3980,18 +4100,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AT61" s="0" t="s">
-        <x:v>172</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:46">
+        <x:v>174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:48">
       <x:c r="A62" s="0">
         <x:v>59</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
         <x:v>6</x:v>
@@ -4000,15 +4120,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:48">
       <x:c r="A63" s="0">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
         <x:v>6</x:v>
@@ -4017,15 +4137,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="K63" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:48">
       <x:c r="A64" s="0">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
         <x:v>7</x:v>
@@ -4034,15 +4154,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L64" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:48">
       <x:c r="A65" s="0">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>7</x:v>
@@ -4051,21 +4171,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="L65" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="AB65" s="0" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="AC65" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="P65" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="V65" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:48">
       <x:c r="A66" s="0">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>7</x:v>
@@ -4074,21 +4194,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="L66" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="P66" s="0" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="V66" s="0" t="s">
-        <x:v>180</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AB66" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="AC66" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:48">
       <x:c r="A67" s="0">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
         <x:v>7</x:v>
@@ -4097,15 +4217,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L67" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:48">
       <x:c r="A68" s="0">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>7</x:v>
@@ -4114,15 +4234,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L68" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:48">
       <x:c r="A69" s="0">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
         <x:v>7</x:v>
@@ -4131,15 +4251,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L69" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:48">
       <x:c r="A70" s="0">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
         <x:v>8</x:v>
@@ -4148,15 +4268,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M70" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:48">
       <x:c r="A71" s="0">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
         <x:v>8</x:v>
@@ -4165,27 +4285,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="M71" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O71" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="P71" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X71" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="AH71" s="0" t="s">
-        <x:v>188</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:46">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:48">
       <x:c r="A72" s="0">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
         <x:v>8</x:v>
@@ -4194,64 +4314,64 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M72" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:48">
       <x:c r="A73" s="0">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D73" s="0">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="M73" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="T73" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="U73" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="W73" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="X73" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AS73" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:48">
       <x:c r="A74" s="0">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="D74" s="0">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M74" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="T74" s="0" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="U74" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="W74" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="X74" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="AS74" s="0" t="s">
-        <x:v>193</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:48">
       <x:c r="A75" s="0">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>8</x:v>
@@ -4260,30 +4380,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="M75" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="P75" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="Q75" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R75" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V75" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AS75" s="0" t="s">
-        <x:v>196</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:46">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:48">
       <x:c r="A76" s="0">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
         <x:v>8</x:v>
@@ -4292,15 +4412,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M76" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:48">
       <x:c r="A77" s="0">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>8</x:v>
@@ -4309,15 +4429,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M77" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:48">
       <x:c r="A78" s="0">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>9</x:v>
@@ -4326,54 +4446,54 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="N78" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O78" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T78" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="U78" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W78" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AA78" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="AB78" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD78" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="AI78" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="AN78" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="AP78" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="AQ78" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS78" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="AT78" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:48">
       <x:c r="A79" s="0">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>9</x:v>
@@ -4382,18 +4502,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="N79" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH79" s="0" t="s">
-        <x:v>207</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:46">
+        <x:v>209</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:48">
       <x:c r="A80" s="0">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
         <x:v>9</x:v>
@@ -4402,18 +4522,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="N80" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U80" s="0" t="s">
-        <x:v>209</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:46">
+        <x:v>211</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:48">
       <x:c r="A81" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
         <x:v>10</x:v>
@@ -4422,30 +4542,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="O81" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R81" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="T81" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="X81" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AA81" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="AO81" s="0" t="s">
-        <x:v>213</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:46">
+        <x:v>215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:48">
       <x:c r="A82" s="0">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
         <x:v>10</x:v>
@@ -4454,42 +4574,42 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="O82" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U82" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="V82" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X82" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="Z82" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="AC82" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="AG82" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="AH82" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AK82" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="AS82" s="0" t="s">
-        <x:v>219</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" spans="1:46">
+        <x:v>221</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:48">
       <x:c r="A83" s="0">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
         <x:v>10</x:v>
@@ -4498,27 +4618,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="O83" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="P83" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S83" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="U83" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="AD83" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" spans="1:46">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:48">
       <x:c r="A84" s="0">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
         <x:v>10</x:v>
@@ -4527,18 +4647,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="O84" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R84" s="0" t="s">
-        <x:v>211</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" spans="1:46">
+        <x:v>213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:48">
       <x:c r="A85" s="0">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>10</x:v>
@@ -4547,15 +4667,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O85" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:48">
       <x:c r="A86" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>10</x:v>
@@ -4564,21 +4684,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="O86" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R86" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="W86" s="0" t="s">
-        <x:v>130</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" spans="1:46">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:48">
       <x:c r="A87" s="0">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>10</x:v>
@@ -4587,15 +4707,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O87" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:48">
       <x:c r="A88" s="0">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
         <x:v>10</x:v>
@@ -4604,15 +4724,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O88" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:48">
       <x:c r="A89" s="0">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
         <x:v>10</x:v>
@@ -4621,15 +4741,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="O89" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:48">
       <x:c r="A90" s="0">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>10</x:v>
@@ -4638,62 +4758,68 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="O90" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T90" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="U90" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:48">
       <x:c r="A91" s="0">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="D91" s="0">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="O91" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="P91" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S91" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="AA91" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="AE91" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="AF91" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH91" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AN91" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="AT91" s="0" t="s">
-        <x:v>233</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:46">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="AU91" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV91" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:48">
       <x:c r="A92" s="0">
         <x:v>89</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
         <x:v>11</x:v>
@@ -4702,18 +4828,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="P92" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG92" s="0" t="s">
-        <x:v>235</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:46">
+        <x:v>237</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:48">
       <x:c r="A93" s="0">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>11</x:v>
@@ -4722,15 +4848,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P93" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:48">
       <x:c r="A94" s="0">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>11</x:v>
@@ -4739,18 +4865,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="P94" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q94" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:48">
       <x:c r="A95" s="0">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>11</x:v>
@@ -4759,39 +4885,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="P95" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q95" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T95" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="U95" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V95" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W95" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AA95" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="AC95" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="AH95" s="0" t="s">
-        <x:v>240</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:46">
+        <x:v>242</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:48">
       <x:c r="A96" s="0">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>11</x:v>
@@ -4800,15 +4926,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P96" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:48">
       <x:c r="A97" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>11</x:v>
@@ -4817,15 +4943,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P97" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:48">
       <x:c r="A98" s="0">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>11</x:v>
@@ -4834,18 +4960,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="P98" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AE98" s="0" t="s">
-        <x:v>244</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:46">
+        <x:v>246</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:48">
       <x:c r="A99" s="0">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>11</x:v>
@@ -4854,15 +4980,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P99" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:48">
       <x:c r="A100" s="0">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>11</x:v>
@@ -4871,15 +4997,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P100" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:48">
       <x:c r="A101" s="0">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>11</x:v>
@@ -4888,15 +5014,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P101" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:48">
       <x:c r="A102" s="0">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>11</x:v>
@@ -4905,15 +5031,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P102" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:48">
       <x:c r="A103" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
         <x:v>11</x:v>
@@ -4922,33 +5048,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="P103" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V103" s="0" t="s">
         <x:v>180</x:v>
       </x:c>
       <x:c r="W103" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="X103" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="Y103" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AJ103" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="AL103" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="X103" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="Y103" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="AJ103" s="0" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="AL103" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" spans="1:46">
+    </x:row>
+    <x:row r="104" spans="1:48">
       <x:c r="A104" s="0">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
         <x:v>11</x:v>
@@ -4957,21 +5083,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="P104" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AA104" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="AF104" s="0" t="s">
-        <x:v>252</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" spans="1:46">
+        <x:v>254</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:48">
       <x:c r="A105" s="0">
         <x:v>102</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>11</x:v>
@@ -4980,27 +5106,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="P105" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q105" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W105" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="AA105" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="AH105" s="0" t="s">
-        <x:v>255</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" spans="1:46">
+        <x:v>257</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:48">
       <x:c r="A106" s="0">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>11</x:v>
@@ -5009,68 +5135,74 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="P106" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T106" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="Z106" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="AD106" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="AE106" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS106" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="AT106" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:48">
       <x:c r="A107" s="0">
         <x:v>104</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D107" s="0">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="P107" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AC107" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="AD107" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AO107" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="AP107" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS107" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="AT107" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU107" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV107" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:48">
       <x:c r="A108" s="0">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
         <x:v>11</x:v>
@@ -5079,15 +5211,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P108" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:48">
       <x:c r="A109" s="0">
         <x:v>106</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>11</x:v>
@@ -5096,33 +5228,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="P109" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q109" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R109" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S109" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X109" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="Y109" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH109" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" spans="1:46">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:48">
       <x:c r="A110" s="0">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
         <x:v>11</x:v>
@@ -5131,15 +5263,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P110" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:48">
       <x:c r="A111" s="0">
         <x:v>108</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>11</x:v>
@@ -5148,18 +5280,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="P111" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U111" s="0" t="s">
-        <x:v>268</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" spans="1:46">
+        <x:v>269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:48">
       <x:c r="A112" s="0">
         <x:v>109</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
         <x:v>11</x:v>
@@ -5168,21 +5300,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="P112" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q112" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S112" s="0" t="s">
-        <x:v>149</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" spans="1:46">
+        <x:v>151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:48">
       <x:c r="A113" s="0">
         <x:v>110</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>11</x:v>
@@ -5191,15 +5323,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="P113" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:48">
       <x:c r="A114" s="0">
         <x:v>111</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>11</x:v>
@@ -5208,27 +5340,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="P114" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Q114" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R114" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S114" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AR114" s="0" t="s">
-        <x:v>272</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" spans="1:46">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:48">
       <x:c r="A115" s="0">
         <x:v>112</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
         <x:v>11</x:v>
@@ -5237,83 +5369,89 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="P115" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S115" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="U115" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="V115" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:48">
       <x:c r="A116" s="0">
         <x:v>113</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D116" s="0">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="Q116" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R116" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S116" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T116" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V116" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="W116" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X116" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y116" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AA116" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="AB116" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AC116" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD116" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AO116" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="AP116" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AR116" s="0" t="s">
-        <x:v>152</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" spans="1:46">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="AU116" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="AV116" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:48">
       <x:c r="A117" s="0">
         <x:v>114</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>12</x:v>
@@ -5322,30 +5460,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="Q117" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="R117" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U117" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="V117" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W117" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X117" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:48">
       <x:c r="A118" s="0">
         <x:v>115</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>12</x:v>
@@ -5354,15 +5492,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q118" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:48">
       <x:c r="A119" s="0">
         <x:v>116</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>12</x:v>
@@ -5371,21 +5509,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="Q119" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T119" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="V119" s="0" t="s">
-        <x:v>275</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" spans="1:46">
+        <x:v>276</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:48">
       <x:c r="A120" s="0">
         <x:v>117</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>12</x:v>
@@ -5394,15 +5532,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q120" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:48">
       <x:c r="A121" s="0">
         <x:v>118</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
         <x:v>12</x:v>
@@ -5411,21 +5549,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="Q121" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X121" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="AN121" s="0" t="s">
-        <x:v>282</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" spans="1:46">
+        <x:v>284</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:48">
       <x:c r="A122" s="0">
         <x:v>119</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
         <x:v>12</x:v>
@@ -5434,18 +5572,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q122" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T122" s="0" t="s">
-        <x:v>150</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" spans="1:46">
+        <x:v>152</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:48">
       <x:c r="A123" s="0">
         <x:v>120</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
         <x:v>13</x:v>
@@ -5454,21 +5592,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R123" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD123" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="AE123" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="124" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:48">
       <x:c r="A124" s="0">
         <x:v>121</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
         <x:v>13</x:v>
@@ -5477,105 +5615,111 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R124" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:48">
       <x:c r="A125" s="0">
         <x:v>122</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D125" s="0">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="R125" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="S125" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U125" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="X125" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="Y125" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AA125" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="AB125" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AC125" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD125" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AE125" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AJ125" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="AK125" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AN125" s="0" t="s">
-        <x:v>81</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="126" spans="1:46">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="AU125" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="AV125" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:48">
       <x:c r="A126" s="0">
         <x:v>123</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D126" s="0">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R126" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="X126" s="0" t="s">
-        <x:v>290</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="127" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:48">
       <x:c r="A127" s="0">
         <x:v>124</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D127" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="R127" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="128" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="X127" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:48">
       <x:c r="A128" s="0">
         <x:v>125</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>13</x:v>
@@ -5584,18 +5728,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R128" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T128" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" spans="1:46">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:48">
       <x:c r="A129" s="0">
         <x:v>126</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
         <x:v>13</x:v>
@@ -5604,15 +5748,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R129" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="130" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:48">
       <x:c r="A130" s="0">
         <x:v>127</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
         <x:v>14</x:v>
@@ -5621,18 +5765,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S130" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T130" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:48">
       <x:c r="A131" s="0">
         <x:v>128</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
         <x:v>14</x:v>
@@ -5641,18 +5785,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S131" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH131" s="0" t="s">
-        <x:v>296</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132" spans="1:46">
+        <x:v>299</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:48">
       <x:c r="A132" s="0">
         <x:v>129</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
         <x:v>14</x:v>
@@ -5661,33 +5805,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="S132" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T132" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U132" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V132" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W132" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X132" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y132" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:48">
       <x:c r="A133" s="0">
         <x:v>130</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
         <x:v>14</x:v>
@@ -5696,18 +5840,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S133" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AB133" s="0" t="s">
-        <x:v>299</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="134" spans="1:46">
+        <x:v>302</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:48">
       <x:c r="A134" s="0">
         <x:v>131</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
         <x:v>14</x:v>
@@ -5716,24 +5860,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="S134" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T134" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG134" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="AM134" s="0" t="s">
-        <x:v>252</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="135" spans="1:46">
+        <x:v>254</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:48">
       <x:c r="A135" s="0">
         <x:v>132</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
         <x:v>14</x:v>
@@ -5742,27 +5886,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="S135" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U135" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="X135" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="Z135" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="AA135" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="136" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:48">
       <x:c r="A136" s="0">
         <x:v>133</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
         <x:v>14</x:v>
@@ -5771,65 +5915,68 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S136" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:48">
       <x:c r="A137" s="0">
         <x:v>134</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D137" s="0">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="S137" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T137" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U137" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X137" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="AB137" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AC137" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD137" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AF137" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="AI137" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="AK137" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="AO137" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="AS137" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="138" spans="1:46">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="AU137" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:48">
       <x:c r="A138" s="0">
         <x:v>135</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>14</x:v>
@@ -5838,18 +5985,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S138" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AA138" s="0" t="s">
-        <x:v>230</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="139" spans="1:46">
+        <x:v>232</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:48">
       <x:c r="A139" s="0">
         <x:v>136</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
         <x:v>14</x:v>
@@ -5858,24 +6005,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="S139" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="T139" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V139" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="AD139" s="0" t="s">
-        <x:v>309</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="140" spans="1:46">
+        <x:v>313</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:48">
       <x:c r="A140" s="0">
         <x:v>137</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
         <x:v>14</x:v>
@@ -5884,24 +6031,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="S140" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U140" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="V140" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W140" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="141" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:48">
       <x:c r="A141" s="0">
         <x:v>138</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
         <x:v>14</x:v>
@@ -5910,24 +6057,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="S141" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AE141" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="AF141" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AO141" s="0" t="s">
-        <x:v>313</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="142" spans="1:46">
+        <x:v>317</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:48">
       <x:c r="A142" s="0">
         <x:v>139</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
         <x:v>14</x:v>
@@ -5936,24 +6083,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="S142" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W142" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="X142" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z142" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="143" spans="1:46">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:48">
       <x:c r="A143" s="0">
         <x:v>140</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
         <x:v>14</x:v>
@@ -5962,15 +6109,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="S143" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="144" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:48">
       <x:c r="A144" s="0">
         <x:v>141</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
         <x:v>15</x:v>
@@ -5979,82 +6126,82 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="T144" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V144" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="W144" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X144" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y144" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AB144" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="AC144" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="145" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:48">
       <x:c r="A145" s="0">
         <x:v>142</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D145" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T145" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="U145" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="V145" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="146" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AA145" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="AD145" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="AN145" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:48">
       <x:c r="A146" s="0">
         <x:v>143</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D146" s="0">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="T146" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="AA146" s="0" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="AD146" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="AN146" s="0" t="s">
-        <x:v>322</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="147" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="U146" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="W146" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:48">
       <x:c r="A147" s="0">
         <x:v>144</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
         <x:v>15</x:v>
@@ -6063,21 +6210,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="T147" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U147" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="W147" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="148" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="V147" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:48">
       <x:c r="A148" s="0">
         <x:v>145</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
         <x:v>15</x:v>
@@ -6086,18 +6233,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="T148" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U148" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="149" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:48">
       <x:c r="A149" s="0">
         <x:v>146</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
         <x:v>15</x:v>
@@ -6106,68 +6253,71 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="T149" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V149" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="W149" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z149" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="AJ149" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="AO149" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="AP149" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AQ149" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS149" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="AT149" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="150" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:48">
       <x:c r="A150" s="0">
         <x:v>147</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D150" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T150" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W150" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="AR150" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="AS150" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="151" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV150" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:48">
       <x:c r="A151" s="0">
         <x:v>148</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
         <x:v>15</x:v>
@@ -6176,50 +6326,53 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="T151" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="U151" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="152" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:48">
       <x:c r="A152" s="0">
         <x:v>149</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D152" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="U152" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V152" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W152" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AB152" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="AO152" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="AP152" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="153" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU152" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:48">
       <x:c r="A153" s="0">
         <x:v>150</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
         <x:v>16</x:v>
@@ -6228,15 +6381,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U153" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="154" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:48">
       <x:c r="A154" s="0">
         <x:v>151</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
         <x:v>16</x:v>
@@ -6245,15 +6398,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="U154" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="155" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:48">
       <x:c r="A155" s="0">
         <x:v>152</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
         <x:v>16</x:v>
@@ -6262,66 +6415,66 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="U155" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V155" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W155" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X155" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y155" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z155" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AB155" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="AC155" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AF155" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="AG155" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH155" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AK155" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="AN155" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="AO155" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AP155" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AR155" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="AS155" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AT155" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="156" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:48">
       <x:c r="A156" s="0">
         <x:v>153</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
         <x:v>16</x:v>
@@ -6330,21 +6483,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="U156" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="V156" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W156" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="157" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:48">
       <x:c r="A157" s="0">
         <x:v>154</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
         <x:v>17</x:v>
@@ -6353,15 +6506,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V157" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="158" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:48">
       <x:c r="A158" s="0">
         <x:v>155</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
         <x:v>17</x:v>
@@ -6370,15 +6523,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V158" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="159" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:48">
       <x:c r="A159" s="0">
         <x:v>156</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
         <x:v>17</x:v>
@@ -6387,47 +6540,50 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="V159" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="W159" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG159" s="0" t="s">
-        <x:v>322</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="160" spans="1:46">
+        <x:v>325</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:48">
       <x:c r="A160" s="0">
         <x:v>157</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D160" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="V160" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AE160" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="AF160" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AT160" s="0" t="s">
-        <x:v>346</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="161" spans="1:46">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="AV160" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:48">
       <x:c r="A161" s="0">
         <x:v>158</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C161" s="0" t="s">
         <x:v>18</x:v>
@@ -6436,24 +6592,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="W161" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X161" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z161" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="AH161" s="0" t="s">
-        <x:v>348</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="162" spans="1:46">
+        <x:v>354</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:48">
       <x:c r="A162" s="0">
         <x:v>159</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
         <x:v>18</x:v>
@@ -6462,15 +6618,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="W162" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="163" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:48">
       <x:c r="A163" s="0">
         <x:v>160</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
         <x:v>18</x:v>
@@ -6479,27 +6635,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="W163" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X163" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AA163" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="AB163" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AE163" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="164" spans="1:46">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:48">
       <x:c r="A164" s="0">
         <x:v>161</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
         <x:v>18</x:v>
@@ -6508,53 +6664,56 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="W164" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AA164" s="0" t="s">
-        <x:v>201</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="165" spans="1:46">
+        <x:v>203</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:48">
       <x:c r="A165" s="0">
         <x:v>162</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D165" s="0">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="W165" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="X165" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z165" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="AA165" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD165" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AR165" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="AT165" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="166" spans="1:46">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="AV165" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:48">
       <x:c r="A166" s="0">
         <x:v>163</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="C166" s="0" t="s">
         <x:v>20</x:v>
@@ -6563,21 +6722,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="Y166" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z166" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS166" s="0" t="s">
-        <x:v>355</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="167" spans="1:46">
+        <x:v>361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:48">
       <x:c r="A167" s="0">
         <x:v>164</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C167" s="0" t="s">
         <x:v>20</x:v>
@@ -6586,18 +6745,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="Y167" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z167" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="168" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:48">
       <x:c r="A168" s="0">
         <x:v>165</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="C168" s="0" t="s">
         <x:v>21</x:v>
@@ -6606,21 +6765,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="Z168" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AI168" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="AK168" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169" spans="1:46">
+        <x:v>130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:48">
       <x:c r="A169" s="0">
         <x:v>166</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="C169" s="0" t="s">
         <x:v>21</x:v>
@@ -6629,15 +6788,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Z169" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:48">
       <x:c r="A170" s="0">
         <x:v>167</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="C170" s="0" t="s">
         <x:v>21</x:v>
@@ -6646,15 +6805,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Z170" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:48">
       <x:c r="A171" s="0">
         <x:v>168</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="C171" s="0" t="s">
         <x:v>21</x:v>
@@ -6663,15 +6822,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Z171" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:48">
       <x:c r="A172" s="0">
         <x:v>169</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C172" s="0" t="s">
         <x:v>22</x:v>
@@ -6680,18 +6839,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AA172" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH172" s="0" t="s">
-        <x:v>255</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173" spans="1:46">
+        <x:v>257</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:48">
       <x:c r="A173" s="0">
         <x:v>170</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="C173" s="0" t="s">
         <x:v>22</x:v>
@@ -6700,27 +6859,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AA173" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AD173" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AI173" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="AL173" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="AO173" s="0" t="s">
-        <x:v>364</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174" spans="1:46">
+        <x:v>370</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:48">
       <x:c r="A174" s="0">
         <x:v>171</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="C174" s="0" t="s">
         <x:v>22</x:v>
@@ -6729,15 +6888,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AA174" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:48">
       <x:c r="A175" s="0">
         <x:v>172</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C175" s="0" t="s">
         <x:v>23</x:v>
@@ -6746,24 +6905,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AB175" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AJ175" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="AK175" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AM175" s="0" t="s">
-        <x:v>368</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176" spans="1:46">
+        <x:v>374</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:48">
       <x:c r="A176" s="0">
         <x:v>173</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C176" s="0" t="s">
         <x:v>24</x:v>
@@ -6772,18 +6931,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AC176" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS176" s="0" t="s">
-        <x:v>370</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="177" spans="1:46">
+        <x:v>376</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:48">
       <x:c r="A177" s="0">
         <x:v>174</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="C177" s="0" t="s">
         <x:v>24</x:v>
@@ -6792,15 +6951,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AC177" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="178" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:48">
       <x:c r="A178" s="0">
         <x:v>175</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="C178" s="0" t="s">
         <x:v>24</x:v>
@@ -6809,15 +6968,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AC178" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:48">
       <x:c r="A179" s="0">
         <x:v>176</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C179" s="0" t="s">
         <x:v>24</x:v>
@@ -6826,21 +6985,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AC179" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AJ179" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="AK179" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="180" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:48">
       <x:c r="A180" s="0">
         <x:v>177</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="C180" s="0" t="s">
         <x:v>24</x:v>
@@ -6849,15 +7008,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AC180" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="181" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:48">
       <x:c r="A181" s="0">
         <x:v>178</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C181" s="0" t="s">
         <x:v>25</x:v>
@@ -6866,18 +7025,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AD181" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AN181" s="0" t="s">
-        <x:v>322</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="182" spans="1:46">
+        <x:v>325</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:48">
       <x:c r="A182" s="0">
         <x:v>179</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="C182" s="0" t="s">
         <x:v>25</x:v>
@@ -6886,21 +7045,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AD182" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH182" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="AT182" s="0" t="s">
-        <x:v>378</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="183" spans="1:46">
+        <x:v>384</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:48">
       <x:c r="A183" s="0">
         <x:v>180</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C183" s="0" t="s">
         <x:v>25</x:v>
@@ -6909,33 +7068,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AD183" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AE183" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AI183" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="AJ183" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AL183" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="AE183" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="AI183" s="0" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="AJ183" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="AL183" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
       <x:c r="AN183" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="AS183" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="184" spans="1:46">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:48">
       <x:c r="A184" s="0">
         <x:v>181</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="C184" s="0" t="s">
         <x:v>25</x:v>
@@ -6944,21 +7103,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AD184" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS184" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="AT184" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="185" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:48">
       <x:c r="A185" s="0">
         <x:v>182</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="C185" s="0" t="s">
         <x:v>25</x:v>
@@ -6967,21 +7126,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AD185" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AE185" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AK185" s="0" t="s">
-        <x:v>215</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="186" spans="1:46">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:48">
       <x:c r="A186" s="0">
         <x:v>183</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C186" s="0" t="s">
         <x:v>26</x:v>
@@ -6990,21 +7149,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AE186" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AF186" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH186" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="187" spans="1:46">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:48">
       <x:c r="A187" s="0">
         <x:v>184</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="C187" s="0" t="s">
         <x:v>27</x:v>
@@ -7013,24 +7172,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AF187" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH187" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AI187" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AO187" s="0" t="s">
-        <x:v>384</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="188" spans="1:46">
+        <x:v>390</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:48">
       <x:c r="A188" s="0">
         <x:v>185</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="C188" s="0" t="s">
         <x:v>27</x:v>
@@ -7039,47 +7198,53 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AF188" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="189" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:48">
       <x:c r="A189" s="0">
         <x:v>186</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="C189" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D189" s="0">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AF189" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AH189" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AJ189" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="AK189" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AN189" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="AO189" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="190" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU189" s="0" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="AV189" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:48">
       <x:c r="A190" s="0">
         <x:v>187</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="C190" s="0" t="s">
         <x:v>27</x:v>
@@ -7088,15 +7253,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AF190" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="191" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:48">
       <x:c r="A191" s="0">
         <x:v>188</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="C191" s="0" t="s">
         <x:v>27</x:v>
@@ -7105,15 +7270,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AF191" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="192" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:48">
       <x:c r="A192" s="0">
         <x:v>189</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="C192" s="0" t="s">
         <x:v>27</x:v>
@@ -7122,15 +7287,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AF192" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="193" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:48">
       <x:c r="A193" s="0">
         <x:v>190</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C193" s="0" t="s">
         <x:v>27</x:v>
@@ -7139,24 +7304,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AF193" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AI193" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="AJ193" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AN193" s="0" t="s">
-        <x:v>339</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="194" spans="1:46">
+        <x:v>345</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:48">
       <x:c r="A194" s="0">
         <x:v>191</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="C194" s="0" t="s">
         <x:v>27</x:v>
@@ -7165,47 +7330,53 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AF194" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="195" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:48">
       <x:c r="A195" s="0">
         <x:v>192</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="C195" s="0" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="D195" s="0">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="AF195" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AI195" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="AJ195" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AK195" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AL195" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AN195" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="196" spans="1:46">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="AU195" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="AV195" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:48">
       <x:c r="A196" s="0">
         <x:v>193</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="C196" s="0" t="s">
         <x:v>27</x:v>
@@ -7214,18 +7385,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AF196" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS196" s="0" t="s">
-        <x:v>394</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="197" spans="1:46">
+        <x:v>401</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:48">
       <x:c r="A197" s="0">
         <x:v>194</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="C197" s="0" t="s">
         <x:v>28</x:v>
@@ -7234,27 +7405,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AG197" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AJ197" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="AK197" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AM197" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="AN197" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="198" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:48">
       <x:c r="A198" s="0">
         <x:v>195</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="C198" s="0" t="s">
         <x:v>28</x:v>
@@ -7263,18 +7434,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AG198" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AN198" s="0" t="s">
-        <x:v>398</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="199" spans="1:46">
+        <x:v>405</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:48">
       <x:c r="A199" s="0">
         <x:v>196</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="C199" s="0" t="s">
         <x:v>29</x:v>
@@ -7283,21 +7454,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AH199" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AI199" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AK199" s="0" t="s">
-        <x:v>128</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="200" spans="1:46">
+        <x:v>130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:48">
       <x:c r="A200" s="0">
         <x:v>197</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="C200" s="0" t="s">
         <x:v>29</x:v>
@@ -7306,21 +7477,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AH200" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AQ200" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="AS200" s="0" t="s">
-        <x:v>205</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="201" spans="1:46">
+        <x:v>207</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:48">
       <x:c r="A201" s="0">
         <x:v>198</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="C201" s="0" t="s">
         <x:v>29</x:v>
@@ -7329,21 +7500,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AH201" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AO201" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="AQ201" s="0" t="s">
-        <x:v>259</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="202" spans="1:46">
+        <x:v>260</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" spans="1:48">
       <x:c r="A202" s="0">
         <x:v>199</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="C202" s="0" t="s">
         <x:v>30</x:v>
@@ -7352,21 +7523,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AI202" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AJ202" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AK202" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="203" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" spans="1:48">
       <x:c r="A203" s="0">
         <x:v>200</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="C203" s="0" t="s">
         <x:v>30</x:v>
@@ -7375,27 +7546,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AI203" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AJ203" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AL203" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="AJ203" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="AL203" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
       <x:c r="AN203" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="AS203" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="204" spans="1:46">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" spans="1:48">
       <x:c r="A204" s="0">
         <x:v>201</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="C204" s="0" t="s">
         <x:v>30</x:v>
@@ -7404,18 +7575,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AI204" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AJ204" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="205" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" spans="1:48">
       <x:c r="A205" s="0">
         <x:v>202</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="C205" s="0" t="s">
         <x:v>30</x:v>
@@ -7424,15 +7595,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AI205" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="206" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" spans="1:48">
       <x:c r="A206" s="0">
         <x:v>203</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="C206" s="0" t="s">
         <x:v>30</x:v>
@@ -7441,18 +7612,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AI206" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AN206" s="0" t="s">
-        <x:v>204</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="207" spans="1:46">
+        <x:v>206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" spans="1:48">
       <x:c r="A207" s="0">
         <x:v>204</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C207" s="0" t="s">
         <x:v>31</x:v>
@@ -7461,21 +7632,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AJ207" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AR207" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="AT207" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="208" spans="1:46">
+        <x:v>155</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" spans="1:48">
       <x:c r="A208" s="0">
         <x:v>205</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="C208" s="0" t="s">
         <x:v>31</x:v>
@@ -7484,18 +7655,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AJ208" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AK208" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="209" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" spans="1:48">
       <x:c r="A209" s="0">
         <x:v>206</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="C209" s="0" t="s">
         <x:v>31</x:v>
@@ -7504,18 +7675,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AJ209" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AL209" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="AL209" s="0" t="s">
-        <x:v>122</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="210" spans="1:46">
+    </x:row>
+    <x:row r="210" spans="1:48">
       <x:c r="A210" s="0">
         <x:v>207</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="C210" s="0" t="s">
         <x:v>32</x:v>
@@ -7524,41 +7695,47 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AK210" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="211" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" spans="1:48">
       <x:c r="A211" s="0">
         <x:v>208</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="C211" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
       <x:c r="D211" s="0">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AK211" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AM211" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="AR211" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="AT211" s="0" t="s">
-        <x:v>153</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="212" spans="1:46">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="AU211" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV211" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" spans="1:48">
       <x:c r="A212" s="0">
         <x:v>209</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="C212" s="0" t="s">
         <x:v>32</x:v>
@@ -7567,21 +7744,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AK212" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AN212" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="AT212" s="0" t="s">
-        <x:v>233</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="213" spans="1:46">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" spans="1:48">
       <x:c r="A213" s="0">
         <x:v>210</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="C213" s="0" t="s">
         <x:v>33</x:v>
@@ -7590,18 +7767,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AL213" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AN213" s="0" t="s">
-        <x:v>140</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="214" spans="1:46">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" spans="1:48">
       <x:c r="A214" s="0">
         <x:v>211</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="C214" s="0" t="s">
         <x:v>34</x:v>
@@ -7610,18 +7787,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AM214" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS214" s="0" t="s">
-        <x:v>419</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="215" spans="1:46">
+        <x:v>426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" spans="1:48">
       <x:c r="A215" s="0">
         <x:v>212</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="C215" s="0" t="s">
         <x:v>35</x:v>
@@ -7630,18 +7807,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AN215" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS215" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="216" spans="1:46">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" spans="1:48">
       <x:c r="A216" s="0">
         <x:v>213</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="C216" s="0" t="s">
         <x:v>35</x:v>
@@ -7650,15 +7827,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AN216" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="217" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" spans="1:48">
       <x:c r="A217" s="0">
         <x:v>214</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="C217" s="0" t="s">
         <x:v>35</x:v>
@@ -7667,15 +7844,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AN217" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="218" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" spans="1:48">
       <x:c r="A218" s="0">
         <x:v>215</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="C218" s="0" t="s">
         <x:v>35</x:v>
@@ -7684,44 +7861,47 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AN218" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="219" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" spans="1:48">
       <x:c r="A219" s="0">
         <x:v>216</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="C219" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="D219" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AO219" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AQ219" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="AR219" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS219" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AT219" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="220" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV219" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" spans="1:48">
       <x:c r="A220" s="0">
         <x:v>217</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="C220" s="0" t="s">
         <x:v>36</x:v>
@@ -7730,24 +7910,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AO220" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AP220" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AR220" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="AS220" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="221" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" spans="1:48">
       <x:c r="A221" s="0">
         <x:v>218</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C221" s="0" t="s">
         <x:v>36</x:v>
@@ -7756,15 +7936,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AO221" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="222" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" spans="1:48">
       <x:c r="A222" s="0">
         <x:v>219</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="C222" s="0" t="s">
         <x:v>36</x:v>
@@ -7773,41 +7953,44 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AO222" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS222" s="0" t="s">
-        <x:v>141</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="223" spans="1:46">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" spans="1:48">
       <x:c r="A223" s="0">
         <x:v>220</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="C223" s="0" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="D223" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AP223" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AR223" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="AS223" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="224" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU223" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" spans="1:48">
       <x:c r="A224" s="0">
         <x:v>221</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="C224" s="0" t="s">
         <x:v>37</x:v>
@@ -7816,55 +7999,61 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AP224" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="225" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" spans="1:48">
       <x:c r="A225" s="0">
         <x:v>222</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="C225" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D225" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AQ225" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="226" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU225" s="0" t="s">
+        <x:v>438</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" spans="1:48">
       <x:c r="A226" s="0">
         <x:v>223</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="C226" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D226" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AQ226" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AR226" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS226" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="227" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU226" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" spans="1:48">
       <x:c r="A227" s="0">
         <x:v>224</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="C227" s="0" t="s">
         <x:v>38</x:v>
@@ -7873,38 +8062,44 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AQ227" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="228" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" spans="1:48">
       <x:c r="A228" s="0">
         <x:v>225</x:v>
       </x:c>
       <x:c r="B228" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="C228" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D228" s="0">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AR228" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS228" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AT228" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="229" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU228" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV228" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" spans="1:48">
       <x:c r="A229" s="0">
         <x:v>226</x:v>
       </x:c>
       <x:c r="B229" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="C229" s="0" t="s">
         <x:v>39</x:v>
@@ -7913,52 +8108,58 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AR229" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="230" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" spans="1:48">
       <x:c r="A230" s="0">
         <x:v>227</x:v>
       </x:c>
       <x:c r="B230" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="C230" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D230" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AR230" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS230" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="231" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU230" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" spans="1:48">
       <x:c r="A231" s="0">
         <x:v>228</x:v>
       </x:c>
       <x:c r="B231" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="C231" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D231" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AR231" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="232" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU231" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" spans="1:48">
       <x:c r="A232" s="0">
         <x:v>229</x:v>
       </x:c>
       <x:c r="B232" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="C232" s="0" t="s">
         <x:v>39</x:v>
@@ -7967,35 +8168,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AR232" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="233" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" spans="1:48">
       <x:c r="A233" s="0">
         <x:v>230</x:v>
       </x:c>
       <x:c r="B233" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="C233" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D233" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AR233" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS233" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="234" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU233" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" spans="1:48">
       <x:c r="A234" s="0">
         <x:v>231</x:v>
       </x:c>
       <x:c r="B234" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="C234" s="0" t="s">
         <x:v>39</x:v>
@@ -8004,32 +8208,35 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AR234" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="235" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" spans="1:48">
       <x:c r="A235" s="0">
         <x:v>232</x:v>
       </x:c>
       <x:c r="B235" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="C235" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D235" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AR235" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="236" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU235" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" spans="1:48">
       <x:c r="A236" s="0">
         <x:v>233</x:v>
       </x:c>
       <x:c r="B236" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="C236" s="0" t="s">
         <x:v>39</x:v>
@@ -8038,61 +8245,73 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AR236" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS236" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="237" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" spans="1:48">
       <x:c r="A237" s="0">
         <x:v>234</x:v>
       </x:c>
       <x:c r="B237" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C237" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D237" s="0">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AR237" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS237" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="238" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU237" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="AV237" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" spans="1:48">
       <x:c r="A238" s="0">
         <x:v>235</x:v>
       </x:c>
       <x:c r="B238" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="C238" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D238" s="0">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AR238" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS238" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AT238" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="239" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU238" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV238" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" spans="1:48">
       <x:c r="A239" s="0">
         <x:v>236</x:v>
       </x:c>
       <x:c r="B239" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="C239" s="0" t="s">
         <x:v>39</x:v>
@@ -8101,18 +8320,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AR239" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS239" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="240" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" spans="1:48">
       <x:c r="A240" s="0">
         <x:v>237</x:v>
       </x:c>
       <x:c r="B240" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="C240" s="0" t="s">
         <x:v>39</x:v>
@@ -8121,21 +8340,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AR240" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS240" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AT240" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="241" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" spans="1:48">
       <x:c r="A241" s="0">
         <x:v>238</x:v>
       </x:c>
       <x:c r="B241" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C241" s="0" t="s">
         <x:v>39</x:v>
@@ -8144,18 +8363,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AR241" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS241" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="242" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" spans="1:48">
       <x:c r="A242" s="0">
         <x:v>239</x:v>
       </x:c>
       <x:c r="B242" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="C242" s="0" t="s">
         <x:v>39</x:v>
@@ -8164,52 +8383,58 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AR242" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="243" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" spans="1:48">
       <x:c r="A243" s="0">
         <x:v>240</x:v>
       </x:c>
       <x:c r="B243" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="C243" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D243" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AR243" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS243" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="244" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV243" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" spans="1:48">
       <x:c r="A244" s="0">
         <x:v>241</x:v>
       </x:c>
       <x:c r="B244" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C244" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D244" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AR244" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="245" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV244" s="0" t="s">
+        <x:v>458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" spans="1:48">
       <x:c r="A245" s="0">
         <x:v>242</x:v>
       </x:c>
       <x:c r="B245" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C245" s="0" t="s">
         <x:v>39</x:v>
@@ -8218,15 +8443,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AR245" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="246" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" spans="1:48">
       <x:c r="A246" s="0">
         <x:v>243</x:v>
       </x:c>
       <x:c r="B246" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="C246" s="0" t="s">
         <x:v>39</x:v>
@@ -8235,38 +8460,44 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AR246" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="247" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" spans="1:48">
       <x:c r="A247" s="0">
         <x:v>244</x:v>
       </x:c>
       <x:c r="B247" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="C247" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D247" s="0">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AR247" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS247" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AT247" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="248" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU247" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV247" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" spans="1:48">
       <x:c r="A248" s="0">
         <x:v>245</x:v>
       </x:c>
       <x:c r="B248" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="C248" s="0" t="s">
         <x:v>39</x:v>
@@ -8275,15 +8506,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AR248" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="249" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" spans="1:48">
       <x:c r="A249" s="0">
         <x:v>246</x:v>
       </x:c>
       <x:c r="B249" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C249" s="0" t="s">
         <x:v>39</x:v>
@@ -8292,52 +8523,61 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AR249" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="250" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" spans="1:48">
       <x:c r="A250" s="0">
         <x:v>247</x:v>
       </x:c>
       <x:c r="B250" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="C250" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D250" s="0">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AR250" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS250" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="251" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU250" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="AV250" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" spans="1:48">
       <x:c r="A251" s="0">
         <x:v>248</x:v>
       </x:c>
       <x:c r="B251" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C251" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="D251" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AR251" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="252" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU251" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" spans="1:48">
       <x:c r="A252" s="0">
         <x:v>249</x:v>
       </x:c>
       <x:c r="B252" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="C252" s="0" t="s">
         <x:v>39</x:v>
@@ -8346,18 +8586,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AR252" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS252" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="253" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" spans="1:48">
       <x:c r="A253" s="0">
         <x:v>250</x:v>
       </x:c>
       <x:c r="B253" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="C253" s="0" t="s">
         <x:v>39</x:v>
@@ -8366,15 +8606,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AR253" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="254" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" spans="1:48">
       <x:c r="A254" s="0">
         <x:v>251</x:v>
       </x:c>
       <x:c r="B254" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="C254" s="0" t="s">
         <x:v>39</x:v>
@@ -8383,15 +8623,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AR254" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="255" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" spans="1:48">
       <x:c r="A255" s="0">
         <x:v>252</x:v>
       </x:c>
       <x:c r="B255" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="C255" s="0" t="s">
         <x:v>40</x:v>
@@ -8400,15 +8640,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AS255" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="256" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" spans="1:48">
       <x:c r="A256" s="0">
         <x:v>253</x:v>
       </x:c>
       <x:c r="B256" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="C256" s="0" t="s">
         <x:v>40</x:v>
@@ -8417,35 +8657,41 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AS256" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="257" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" spans="1:48">
       <x:c r="A257" s="0">
         <x:v>254</x:v>
       </x:c>
       <x:c r="B257" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="C257" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D257" s="0">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AS257" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AT257" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="258" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU257" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV257" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" spans="1:48">
       <x:c r="A258" s="0">
         <x:v>255</x:v>
       </x:c>
       <x:c r="B258" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C258" s="0" t="s">
         <x:v>40</x:v>
@@ -8454,15 +8700,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AS258" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="259" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" spans="1:48">
       <x:c r="A259" s="0">
         <x:v>256</x:v>
       </x:c>
       <x:c r="B259" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="C259" s="0" t="s">
         <x:v>40</x:v>
@@ -8471,49 +8717,58 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AS259" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="260" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260" spans="1:48">
       <x:c r="A260" s="0">
         <x:v>257</x:v>
       </x:c>
       <x:c r="B260" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="C260" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D260" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AS260" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="261" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU260" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" spans="1:48">
       <x:c r="A261" s="0">
         <x:v>258</x:v>
       </x:c>
       <x:c r="B261" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="C261" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D261" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AS261" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="262" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU261" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="AV261" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" spans="1:48">
       <x:c r="A262" s="0">
         <x:v>259</x:v>
       </x:c>
       <x:c r="B262" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="C262" s="0" t="s">
         <x:v>40</x:v>
@@ -8522,15 +8777,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AS262" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="263" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" spans="1:48">
       <x:c r="A263" s="0">
         <x:v>260</x:v>
       </x:c>
       <x:c r="B263" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="C263" s="0" t="s">
         <x:v>40</x:v>
@@ -8539,18 +8794,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AS263" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AT263" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="264" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" spans="1:48">
       <x:c r="A264" s="0">
         <x:v>261</x:v>
       </x:c>
       <x:c r="B264" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C264" s="0" t="s">
         <x:v>40</x:v>
@@ -8559,35 +8814,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AS264" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="265" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" spans="1:48">
       <x:c r="A265" s="0">
         <x:v>262</x:v>
       </x:c>
       <x:c r="B265" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="C265" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="D265" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AS265" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AT265" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="266" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV265" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" spans="1:48">
       <x:c r="A266" s="0">
         <x:v>263</x:v>
       </x:c>
       <x:c r="B266" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="C266" s="0" t="s">
         <x:v>40</x:v>
@@ -8596,18 +8854,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AS266" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AT266" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="267" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" spans="1:48">
       <x:c r="A267" s="0">
         <x:v>264</x:v>
       </x:c>
       <x:c r="B267" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="C267" s="0" t="s">
         <x:v>40</x:v>
@@ -8616,15 +8874,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AS267" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="268" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" spans="1:48">
       <x:c r="A268" s="0">
         <x:v>265</x:v>
       </x:c>
       <x:c r="B268" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="C268" s="0" t="s">
         <x:v>41</x:v>
@@ -8633,32 +8891,35 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AT268" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="269" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" spans="1:48">
       <x:c r="A269" s="0">
         <x:v>266</x:v>
       </x:c>
       <x:c r="B269" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="C269" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D269" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AT269" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="270" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV269" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" spans="1:48">
       <x:c r="A270" s="0">
         <x:v>267</x:v>
       </x:c>
       <x:c r="B270" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="C270" s="0" t="s">
         <x:v>41</x:v>
@@ -8667,32 +8928,35 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AT270" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="271" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" spans="1:48">
       <x:c r="A271" s="0">
         <x:v>268</x:v>
       </x:c>
       <x:c r="B271" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="C271" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D271" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AT271" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="272" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV271" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" spans="1:48">
       <x:c r="A272" s="0">
         <x:v>269</x:v>
       </x:c>
       <x:c r="B272" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="C272" s="0" t="s">
         <x:v>41</x:v>
@@ -8701,83 +8965,101 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AT272" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="273" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" spans="1:48">
       <x:c r="A273" s="0">
         <x:v>270</x:v>
       </x:c>
       <x:c r="B273" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="C273" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D273" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AT273" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="274" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU273" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV273" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" spans="1:48">
       <x:c r="A274" s="0">
         <x:v>271</x:v>
       </x:c>
       <x:c r="B274" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="C274" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D274" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AT274" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="275" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU274" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" spans="1:48">
       <x:c r="A275" s="0">
         <x:v>272</x:v>
       </x:c>
       <x:c r="B275" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="C275" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D275" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AT275" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="276" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV275" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" spans="1:48">
       <x:c r="A276" s="0">
         <x:v>273</x:v>
       </x:c>
       <x:c r="B276" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="C276" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D276" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AT276" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="277" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU276" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV276" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" spans="1:48">
       <x:c r="A277" s="0">
         <x:v>274</x:v>
       </x:c>
       <x:c r="B277" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="C277" s="0" t="s">
         <x:v>41</x:v>
@@ -8786,15 +9068,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AT277" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="278" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" spans="1:48">
       <x:c r="A278" s="0">
         <x:v>275</x:v>
       </x:c>
       <x:c r="B278" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="C278" s="0" t="s">
         <x:v>41</x:v>
@@ -8803,32 +9085,35 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AT278" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="279" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" spans="1:48">
       <x:c r="A279" s="0">
         <x:v>276</x:v>
       </x:c>
       <x:c r="B279" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="C279" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D279" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AT279" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="280" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV279" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" spans="1:48">
       <x:c r="A280" s="0">
         <x:v>277</x:v>
       </x:c>
       <x:c r="B280" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="C280" s="0" t="s">
         <x:v>41</x:v>
@@ -8837,15 +9122,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AT280" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="281" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" spans="1:48">
       <x:c r="A281" s="0">
         <x:v>278</x:v>
       </x:c>
       <x:c r="B281" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="C281" s="0" t="s">
         <x:v>41</x:v>
@@ -8854,66 +9139,78 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AT281" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="282" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" spans="1:48">
       <x:c r="A282" s="0">
         <x:v>279</x:v>
       </x:c>
       <x:c r="B282" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="C282" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D282" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AT282" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="283" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV282" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" spans="1:48">
       <x:c r="A283" s="0">
         <x:v>280</x:v>
       </x:c>
       <x:c r="B283" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="C283" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D283" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AT283" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="284" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV283" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" spans="1:48">
       <x:c r="A284" s="0">
         <x:v>281</x:v>
       </x:c>
       <x:c r="B284" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="C284" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="D284" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AT284" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="285" spans="1:46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AU284" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV284" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" spans="1:48">
       <x:c r="A285" s="0">
         <x:v>282</x:v>
       </x:c>
       <x:c r="B285" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="C285" s="0" t="s">
         <x:v>41</x:v>
@@ -8922,7 +9219,354 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AT285" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" spans="1:48">
+      <x:c r="A286" s="0">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="B286" s="0" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="C286" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D286" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AU286" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV286" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" spans="1:48">
+      <x:c r="A287" s="0">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="B287" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="C287" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D287" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AU287" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV287" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" spans="1:48">
+      <x:c r="A288" s="0">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B288" s="0" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="C288" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D288" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU288" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" spans="1:48">
+      <x:c r="A289" s="0">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B289" s="0" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="C289" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D289" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AU289" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV289" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" spans="1:48">
+      <x:c r="A290" s="0">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B290" s="0" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="C290" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D290" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AU290" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV290" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" spans="1:48">
+      <x:c r="A291" s="0">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="B291" s="0" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="C291" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D291" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AU291" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV291" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" spans="1:48">
+      <x:c r="A292" s="0">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="B292" s="0" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="C292" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D292" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AU292" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV292" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" spans="1:48">
+      <x:c r="A293" s="0">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="B293" s="0" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="C293" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D293" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AU293" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV293" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" spans="1:48">
+      <x:c r="A294" s="0">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B294" s="0" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="C294" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D294" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AU294" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="AV294" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" spans="1:48">
+      <x:c r="A295" s="0">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="B295" s="0" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="C295" s="0" t="s">
         <x:v>43</x:v>
+      </x:c>
+      <x:c r="D295" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV295" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" spans="1:48">
+      <x:c r="A296" s="0">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B296" s="0" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="C296" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D296" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV296" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297" spans="1:48">
+      <x:c r="A297" s="0">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="B297" s="0" t="s">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="C297" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D297" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV297" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" spans="1:48">
+      <x:c r="A298" s="0">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="B298" s="0" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="C298" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D298" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV298" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" spans="1:48">
+      <x:c r="A299" s="0">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="B299" s="0" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="C299" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D299" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV299" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" spans="1:48">
+      <x:c r="A300" s="0">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B300" s="0" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="C300" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D300" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV300" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" spans="1:48">
+      <x:c r="A301" s="0">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="B301" s="0" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="C301" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D301" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV301" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" spans="1:48">
+      <x:c r="A302" s="0">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="B302" s="0" t="s">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="C302" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D302" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV302" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" spans="1:48">
+      <x:c r="A303" s="0">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B303" s="0" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="C303" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D303" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV303" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" spans="1:48">
+      <x:c r="A304" s="0">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B304" s="0" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="C304" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D304" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AV304" s="0" t="s">
+        <x:v>45</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
